--- a/KatalonData/ABPTestDataDemo/PaymentsCC_Demo.xlsx
+++ b/KatalonData/ABPTestDataDemo/PaymentsCC_Demo.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="85">
   <si>
     <t>Result</t>
   </si>
@@ -290,6 +290,42 @@
   </si>
   <si>
     <t>Thu Dec 18 15:18:49 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 23 14:38:12 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 23 14:38:59 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 23 14:39:33 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 23 15:42:19 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 23 15:44:49 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 23 15:52:07 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Dec 23 22:15:10 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 24 16:06:05 IST 2025</t>
+  </si>
+  <si>
+    <t>Thu Dec 25 19:29:47 IST 2025</t>
+  </si>
+  <si>
+    <t>Thu Dec 25 21:09:20 IST 2025</t>
+  </si>
+  <si>
+    <t>Thu Dec 25 22:25:11 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 18:42:07 IST 2025</t>
   </si>
 </sst>
 </file>
@@ -727,7 +763,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -755,7 +791,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
@@ -778,10 +814,10 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
@@ -955,7 +991,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1093,7 +1129,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1270,7 +1306,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1343,7 +1379,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1488,10 +1524,10 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1700,7 +1736,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/ABPTestDataDemo/PaymentsCC_Demo.xlsx
+++ b/KatalonData/ABPTestDataDemo/PaymentsCC_Demo.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="133">
   <si>
     <t>Result</t>
   </si>
@@ -326,6 +326,150 @@
   </si>
   <si>
     <t>Fri Dec 26 18:42:07 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 18:15:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 18:20:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 18:27:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 18:33:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 18:40:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 19:18:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 19:24:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 19:32:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 19:38:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 19:44:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 19:52:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 19:58:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:04:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:10:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:21:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:54:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:55:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:56:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:56:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:57:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:58:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:59:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 22:00:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 22:01:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 22:02:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 22:02:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 22:03:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 22:04:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 22:06:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 22:07:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 22:08:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 22:08:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 22:09:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 22:10:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 22:11:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 22:12:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 22:12:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 22:13:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 22:14:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 23:55:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 23:56:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 23:57:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 23:58:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 23:58:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:53:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:54:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:55:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:57:03 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -723,7 +867,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -759,11 +903,11 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
-        <v>73</v>
+      <c r="B2" t="s" s="0">
+        <v>109</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -787,11 +931,11 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>74</v>
+      <c r="A3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>110</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
@@ -813,11 +957,11 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B4" t="s">
-        <v>75</v>
+      <c r="B4" t="s" s="0">
+        <v>111</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
@@ -848,7 +992,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CFB1CD1-F3B6-43AC-8580-D3EB244DA395}">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="7" max="7" customWidth="true" width="11.36328125" collapsed="true"/>
@@ -906,11 +1050,11 @@
       </c>
     </row>
     <row ht="130.5" r="2" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
-        <v>72</v>
+      <c r="B2" t="s" s="0">
+        <v>99</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -949,7 +1093,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A934BCA2-85F5-4C93-BBEE-2C380B06E8FD}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="7" max="7" customWidth="true" width="15.453125" collapsed="true"/>
@@ -979,19 +1123,19 @@
       <c r="G1" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
-        <v>82</v>
+      <c r="B2" t="s" s="0">
+        <v>126</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1003,22 +1147,22 @@
       <c r="F2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>37</v>
       </c>
       <c r="D3" s="7" t="s">
@@ -1030,22 +1174,22 @@
       <c r="F3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G3" t="str">
+      <c r="G3" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" t="s" s="0">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>38</v>
       </c>
       <c r="D4" s="7" t="s">
@@ -1057,11 +1201,11 @@
       <c r="F4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G4" t="str">
+      <c r="G4" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" t="s" s="0">
         <v>34</v>
       </c>
     </row>
@@ -1083,7 +1227,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0B956F6-C214-41E0-9C06-CEBF82C79B1D}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="7" max="7" bestFit="true" customWidth="true" width="14.90625" collapsed="true"/>
@@ -1114,22 +1258,22 @@
       <c r="G1" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
-        <v>81</v>
+      <c r="B2" t="s" s="0">
+        <v>125</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1141,25 +1285,25 @@
       <c r="F2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>40</v>
       </c>
       <c r="D3" s="7" t="s">
@@ -1171,14 +1315,14 @@
       <c r="F3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G3" t="str">
+      <c r="G3" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" t="s" s="0">
         <v>32</v>
       </c>
     </row>
@@ -1189,7 +1333,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14FA0791-CEBE-4D11-B2A1-F3F80E94D9F6}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="9" max="9" bestFit="true" customWidth="true" width="20.453125" collapsed="true"/>
@@ -1218,21 +1362,21 @@
       <c r="G1" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>59</v>
       </c>
       <c r="C2" s="9"/>
@@ -1245,17 +1389,17 @@
       <c r="F2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>41</v>
       </c>
     </row>
@@ -1266,7 +1410,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42D40E85-2D41-457A-88AE-C55FF8092C53}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -1291,22 +1435,22 @@
       <c r="G1" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
-        <v>83</v>
+      <c r="B2" t="s" s="0">
+        <v>127</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1318,17 +1462,17 @@
       <c r="F2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>41</v>
       </c>
     </row>
@@ -1339,7 +1483,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CCD7964-6EA7-47FC-8316-5BB19CD71397}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -1364,22 +1508,22 @@
       <c r="G1" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
-        <v>84</v>
+      <c r="B2" t="s" s="0">
+        <v>128</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1391,17 +1535,17 @@
       <c r="F2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>41</v>
       </c>
     </row>
@@ -1412,7 +1556,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{971A235C-1EB8-4FB4-A052-AC25C4AD1D51}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -1437,18 +1581,18 @@
       <c r="G1" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>38</v>
       </c>
       <c r="D2" s="7" t="s">
@@ -1460,14 +1604,14 @@
       <c r="F2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>36</v>
       </c>
     </row>
@@ -1478,7 +1622,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24D17964-3C9A-4128-9E79-065C6162AEA0}">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="12" max="12" customWidth="true" width="9.81640625" collapsed="true"/>
@@ -1523,11 +1667,11 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B2" t="s">
-        <v>79</v>
+      <c r="B2" t="s" s="0">
+        <v>132</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1557,10 +1701,10 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>14</v>
       </c>
       <c r="C3" s="3"/>
@@ -1583,10 +1727,10 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>15</v>
       </c>
       <c r="C4" s="3"/>
@@ -1615,7 +1759,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F3F653-DA45-4F17-B585-55D2A689218D}">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="31.0" collapsed="true"/>
@@ -1658,10 +1802,10 @@
       <c r="L1" s="4"/>
     </row>
     <row ht="145" r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>48</v>
       </c>
       <c r="C2" s="3"/>
@@ -1696,7 +1840,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C63CEF1E-9472-4171-9CD3-FA3B036F7CBF}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -1732,11 +1876,11 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>78</v>
+      <c r="A2" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>121</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1760,11 +1904,11 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
-        <v>53</v>
+      <c r="B3" t="s" s="0">
+        <v>122</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
@@ -1786,11 +1930,11 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>54</v>
+      <c r="B4" t="s" s="0">
+        <v>123</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
@@ -1818,7 +1962,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{279D9BFE-7E90-4AE5-8638-D512C4CC008B}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -1854,10 +1998,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>49</v>
       </c>
       <c r="C2" s="3"/>
@@ -1882,10 +2026,10 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>50</v>
       </c>
       <c r="C3" s="3"/>
@@ -1908,10 +2052,10 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>51</v>
       </c>
       <c r="C4" s="3"/>
@@ -1940,7 +2084,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C743C20-9154-41EC-9178-39729EDF45F3}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -1976,10 +2120,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>55</v>
       </c>
       <c r="C2" s="3"/>
@@ -2010,7 +2154,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2AC4ABD-97C1-4B0A-A78A-1F57EE1A6D5C}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="42.90625" collapsed="true"/>
@@ -2052,10 +2196,10 @@
       </c>
     </row>
     <row customHeight="1" ht="231" r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>70</v>
       </c>
       <c r="C2" s="3"/>
@@ -2089,7 +2233,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62A0D7E3-B8FB-4BA8-A147-CA4665BD31FB}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:11" x14ac:dyDescent="0.35">
@@ -2128,10 +2272,10 @@
       </c>
     </row>
     <row ht="362.5" r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>47</v>
       </c>
       <c r="C2" s="3"/>
@@ -2165,7 +2309,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CB2C77F-A6BC-4072-8D66-A2FB7943F35E}">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" style="10" width="8.7265625" collapsed="true"/>

--- a/KatalonData/ABPTestDataDemo/PaymentsCC_Demo.xlsx
+++ b/KatalonData/ABPTestDataDemo/PaymentsCC_Demo.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\ABPTestDataDemo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{1433B12F-2A0A-4BE1-8C5A-90D3F77E72E1}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97F12B75-AFD9-42A7-ADBF-3850D6DA534B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="6" firstSheet="6" windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-110"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="VerifySuccessfulPaymentCCNoCF" r:id="rId1" sheetId="1"/>
-    <sheet name="VerifyCFVerbiageOnRPCCDCF" r:id="rId2" sheetId="4"/>
-    <sheet name="VerifyStaticTextOnRecieptCC" r:id="rId3" sheetId="5"/>
-    <sheet name="VerifySuccessfulPaymentCCSCF" r:id="rId4" sheetId="2"/>
-    <sheet name="VerifySuccessfulPaymentCCDCF" r:id="rId5" sheetId="3"/>
-    <sheet name="VerifySuccessfulPaymentSPMCCDCF" r:id="rId6" sheetId="9"/>
-    <sheet name="UiVerificationSPPaymentMethodCC" r:id="rId7" sheetId="10"/>
-    <sheet name="VerifyStaticTextOnPPCCDCF" r:id="rId8" sheetId="6"/>
-    <sheet name="UIVerifySelectPaymentMethodCC" r:id="rId9" sheetId="7"/>
-    <sheet name="CreateVerifyDeleteCCPM" r:id="rId10" sheetId="8"/>
-    <sheet name="CreateSPDCFCC_IPDeferred" r:id="rId11" sheetId="11"/>
-    <sheet name="CreateSPDCFCC_IPDailyNOP" r:id="rId12" sheetId="12"/>
-    <sheet name="CreateSPDCFCC_IPDailyIA" r:id="rId13" sheetId="13"/>
-    <sheet name="CreateSPDCFCC_RecDaily" r:id="rId14" sheetId="14"/>
-    <sheet name="CreateSPDCFCC_RecDeferred" r:id="rId15" sheetId="15"/>
-    <sheet name="CreateSPDCFCC_AutomaticPayment" r:id="rId16" sheetId="16"/>
+    <sheet name="VerifySuccessfulPaymentCCNoCF" sheetId="1" r:id="rId1"/>
+    <sheet name="VerifyCFVerbiageOnRPCCDCF" sheetId="4" r:id="rId2"/>
+    <sheet name="VerifyStaticTextOnRecieptCC" sheetId="5" r:id="rId3"/>
+    <sheet name="VerifySuccessfulPaymentCCSCF" sheetId="2" r:id="rId4"/>
+    <sheet name="VerifySuccessfulPaymentCCDCF" sheetId="3" r:id="rId5"/>
+    <sheet name="VerifySuccessfulPaymentSPMCCDCF" sheetId="9" r:id="rId6"/>
+    <sheet name="UiVerificationSPPaymentMethodCC" sheetId="10" r:id="rId7"/>
+    <sheet name="VerifyStaticTextOnPPCCDCF" sheetId="6" r:id="rId8"/>
+    <sheet name="UIVerifySelectPaymentMethodCC" sheetId="7" r:id="rId9"/>
+    <sheet name="CreateVerifyDeleteCCPM" sheetId="8" r:id="rId10"/>
+    <sheet name="CreateSPDCFCC_IPDeferred" sheetId="11" r:id="rId11"/>
+    <sheet name="CreateSPDCFCC_IPDailyNOP" sheetId="12" r:id="rId12"/>
+    <sheet name="CreateSPDCFCC_IPDailyIA" sheetId="13" r:id="rId13"/>
+    <sheet name="CreateSPDCFCC_RecDaily" sheetId="14" r:id="rId14"/>
+    <sheet name="CreateSPDCFCC_RecDeferred" sheetId="15" r:id="rId15"/>
+    <sheet name="CreateSPDCFCC_AutomaticPayment" sheetId="16" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="71">
   <si>
     <t>Result</t>
   </si>
@@ -184,18 +184,6 @@
     <t>NumberOfPayments</t>
   </si>
   <si>
-    <t>Mon Sep 08 23:14:30 IST 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 25 23:24:17 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 00:21:26 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Oct 30 09:36:21 IST 2025</t>
-  </si>
-  <si>
     <t>Thu Oct 30 09:38:46 IST 2025</t>
   </si>
   <si>
@@ -211,31 +199,10 @@
     <t>Thu Oct 30 09:43:40 IST 2025</t>
   </si>
   <si>
-    <t>Thu Oct 30 10:07:10 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Oct 30 10:09:46 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Oct 30 10:12:28 IST 2025</t>
-  </si>
-  <si>
     <t>Thu Oct 30 10:49:47 IST 2025</t>
   </si>
   <si>
-    <t>Fri Oct 31 15:02:51 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Oct 31 15:05:37 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Oct 31 15:08:30 IST 2025</t>
-  </si>
-  <si>
     <t>Mon Nov 03 21:43:50 IST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 03 22:50:54 IST 2025</t>
   </si>
   <si>
     <t>708 36TH AVE NW</t>
@@ -265,12 +232,6 @@
 United States</t>
   </si>
   <si>
-    <t>Mon Dec 15 23:39:15 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Dec 16 19:22:28 IST 2025</t>
-  </si>
-  <si>
     <t>Name Appearing on Card:,TABATHA MCGALLIARD,
 Card Type:,	Mastercard Debit,
 Card Number:,	51****0035,
@@ -280,174 +241,12 @@
 Country:,	UNITED STATES,</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Tue Dec 16 19:24:38 IST 2025</t>
   </si>
   <si>
-    <t>Thu Dec 18 15:06:18 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Dec 18 15:18:49 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Dec 23 14:38:12 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Dec 23 14:38:59 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Dec 23 14:39:33 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Dec 23 15:42:19 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Dec 23 15:44:49 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Dec 23 15:52:07 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Dec 23 22:15:10 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Dec 24 16:06:05 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Dec 25 19:29:47 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Dec 25 21:09:20 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Dec 25 22:25:11 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 18:42:07 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 18:15:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 18:20:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 18:27:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 18:33:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 18:40:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 19:18:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 19:24:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 19:32:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 19:38:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 19:44:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 19:52:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 19:58:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 20:04:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 20:10:17 IST 2026</t>
-  </si>
-  <si>
     <t>Fri Jul 03 20:21:30 IST 2026</t>
   </si>
   <si>
-    <t>Fri Jul 03 21:54:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:55:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:56:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:56:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:57:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:58:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:59:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 22:00:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 22:01:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 22:02:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 22:02:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 22:03:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 22:04:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 22:06:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 22:07:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 22:08:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 22:08:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 22:09:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 22:10:40 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 22:11:10 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 22:12:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 22:12:43 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 22:13:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 22:14:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 06 23:55:25 IST 2026</t>
-  </si>
-  <si>
     <t>Mon Jul 06 23:56:58 IST 2026</t>
   </si>
   <si>
@@ -460,16 +259,31 @@
     <t>Mon Jul 06 23:58:42 IST 2026</t>
   </si>
   <si>
-    <t>Tue Jul 07 00:53:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jul 07 00:54:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jul 07 00:55:48 IST 2026</t>
-  </si>
-  <si>
     <t>Tue Jul 07 00:57:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 22 15:05:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 22 15:09:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 22 15:10:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 22 15:15:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 22 15:15:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 22 15:16:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 22 15:47:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 24 18:03:01 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -548,51 +362,51 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="14">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="2" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyBorder="1" applyNumberFormat="1" borderId="2" fillId="0" fontId="0" numFmtId="2" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="2" fillId="0" fontId="0" numFmtId="2" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -609,10 +423,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -647,7 +461,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -682,7 +496,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -776,21 +590,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -807,7 +621,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -859,18 +673,22 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="25.0"/>
+    <col min="3" max="3" customWidth="true" width="22.08984375"/>
+  </cols>
   <sheetData>
-    <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -907,7 +725,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>109</v>
+        <v>63</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -932,10 +750,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>110</v>
+        <v>64</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
@@ -958,10 +776,10 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s" s="0">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>111</v>
+        <v>65</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
@@ -983,7 +801,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -991,7 +809,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CFB1CD1-F3B6-43AC-8580-D3EB244DA395}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CFB1CD1-F3B6-43AC-8580-D3EB244DA395}">
   <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1002,7 +820,7 @@
     <col min="15" max="15" customWidth="true" width="12.36328125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="29" r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1049,12 +867,12 @@
         <v>26</v>
       </c>
     </row>
-    <row ht="130.5" r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1077,22 +895,22 @@
         <v>6</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
       <c r="O2" s="9" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A934BCA2-85F5-4C93-BBEE-2C380B06E8FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A934BCA2-85F5-4C93-BBEE-2C380B06E8FD}">
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1135,7 +953,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>126</v>
+        <v>59</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1220,13 +1038,13 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0B956F6-C214-41E0-9C06-CEBF82C79B1D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0B956F6-C214-41E0-9C06-CEBF82C79B1D}">
   <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1273,7 +1091,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1327,12 +1145,12 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14FA0791-CEBE-4D11-B2A1-F3F80E94D9F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14FA0791-CEBE-4D11-B2A1-F3F80E94D9F6}">
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1377,7 +1195,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1404,12 +1222,12 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42D40E85-2D41-457A-88AE-C55FF8092C53}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42D40E85-2D41-457A-88AE-C55FF8092C53}">
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -1450,7 +1268,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>127</v>
+        <v>60</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1477,12 +1295,12 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CCD7964-6EA7-47FC-8316-5BB19CD71397}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CCD7964-6EA7-47FC-8316-5BB19CD71397}">
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -1523,7 +1341,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>128</v>
+        <v>61</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1550,12 +1368,12 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{971A235C-1EB8-4FB4-A052-AC25C4AD1D51}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{971A235C-1EB8-4FB4-A052-AC25C4AD1D51}">
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -1616,19 +1434,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24D17964-3C9A-4128-9E79-065C6162AEA0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24D17964-3C9A-4128-9E79-065C6162AEA0}">
   <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="12" max="12" customWidth="true" width="9.81640625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="29" r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1671,7 +1489,7 @@
         <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>132</v>
+        <v>70</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1753,19 +1571,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F3F653-DA45-4F17-B585-55D2A689218D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F3F653-DA45-4F17-B585-55D2A689218D}">
   <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="31.0" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="29" r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1801,12 +1619,12 @@
       </c>
       <c r="L1" s="4"/>
     </row>
-    <row ht="145" r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="145" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7" t="s">
@@ -1834,16 +1652,19 @@
       <c r="L2" s="5"/>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C63CEF1E-9472-4171-9CD3-FA3B036F7CBF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C63CEF1E-9472-4171-9CD3-FA3B036F7CBF}">
   <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" customWidth="true" width="19.81640625"/>
+  </cols>
   <sheetData>
-    <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1877,10 +1698,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>121</v>
+        <v>66</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1908,7 +1729,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>122</v>
+        <v>67</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
@@ -1934,7 +1755,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>123</v>
+        <v>68</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
@@ -1956,16 +1777,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{279D9BFE-7E90-4AE5-8638-D512C4CC008B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{279D9BFE-7E90-4AE5-8638-D512C4CC008B}">
   <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2002,7 +1823,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2030,7 +1851,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
@@ -2056,7 +1877,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
@@ -2078,16 +1899,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C743C20-9154-41EC-9178-39729EDF45F3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C743C20-9154-41EC-9178-39729EDF45F3}">
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2124,7 +1945,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2148,19 +1969,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2AC4ABD-97C1-4B0A-A78A-1F57EE1A6D5C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2AC4ABD-97C1-4B0A-A78A-1F57EE1A6D5C}">
   <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="42.90625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="29" r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2195,12 +2016,12 @@
         <v>19</v>
       </c>
     </row>
-    <row customHeight="1" ht="231" r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="231" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7" t="s">
@@ -2223,20 +2044,20 @@
         <v>6</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62A0D7E3-B8FB-4BA8-A147-CA4665BD31FB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62A0D7E3-B8FB-4BA8-A147-CA4665BD31FB}">
   <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2271,12 +2092,12 @@
         <v>19</v>
       </c>
     </row>
-    <row ht="362.5" r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7" t="s">
@@ -2303,12 +2124,12 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CB2C77F-A6BC-4072-8D66-A2FB7943F35E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CB2C77F-A6BC-4072-8D66-A2FB7943F35E}">
   <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2371,7 +2192,7 @@
         <v>26</v>
       </c>
     </row>
-    <row ht="333.5" r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="333.5" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>10</v>
       </c>
@@ -2399,22 +2220,22 @@
         <v>6</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M2" s="8">
         <v>28601</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>